--- a/artfynd/A 56194-2021 artfynd.xlsx
+++ b/artfynd/A 56194-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56194-2021 artfynd.xlsx
+++ b/artfynd/A 56194-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>89585509</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416245.9559044077</v>
+        <v>416246</v>
       </c>
       <c r="R2" t="n">
-        <v>7056575.879490032</v>
+        <v>7056576</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>89585520</v>
       </c>
       <c r="B3" t="n">
-        <v>90339</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416271.0571899801</v>
+        <v>416271</v>
       </c>
       <c r="R3" t="n">
-        <v>7056564.984895117</v>
+        <v>7056565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89585506</v>
+        <v>89585445</v>
       </c>
       <c r="B4" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416245.9559044077</v>
+        <v>416250</v>
       </c>
       <c r="R4" t="n">
-        <v>7056575.879490032</v>
+        <v>7056474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,21 +945,11 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,6 +958,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1023,37 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89585531</v>
+        <v>89585461</v>
       </c>
       <c r="B5" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220686</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416163.1420358297</v>
+        <v>416250</v>
       </c>
       <c r="R5" t="n">
-        <v>7056796.030482454</v>
+        <v>7056431</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,21 +1051,11 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,6 +1064,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Rönn</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,37 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89585461</v>
+        <v>89585506</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416250.1493445268</v>
+        <v>416246</v>
       </c>
       <c r="R6" t="n">
-        <v>7056431.194693265</v>
+        <v>7056576</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,21 +1157,11 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,11 +1170,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1260,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89585467</v>
+        <v>89585531</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>220686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416301.7774677196</v>
+        <v>416163</v>
       </c>
       <c r="R7" t="n">
-        <v>7056497.002589021</v>
+        <v>7056796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,21 +1258,11 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1356,11 +1271,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1381,15 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89585495</v>
+        <v>89585467</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416248.0321694466</v>
+        <v>416302</v>
       </c>
       <c r="R8" t="n">
-        <v>7056469.062936906</v>
+        <v>7056497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,21 +1359,11 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1480,7 +1375,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Rönn</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1502,37 +1397,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89585445</v>
+        <v>89585495</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416249.9419309934</v>
+        <v>416248</v>
       </c>
       <c r="R9" t="n">
-        <v>7056473.905779801</v>
+        <v>7056469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,21 +1465,11 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1601,7 +1481,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Rönn</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 56194-2021 artfynd.xlsx
+++ b/artfynd/A 56194-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585445</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585461</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585506</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585531</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585467</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,8 +1540,23 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89585495</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>